--- a/Monitoría 202601.xlsx
+++ b/Monitoría 202601.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\OneDrive\Escritorio\Monitoria-202601\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67E5EF0-7D05-4698-8D2B-013376C5881F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DECE266-7497-4BDB-9A68-E3DAECA14EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3C32DDC5-944F-4023-957D-E29A0EB9D475}"/>
   </bookViews>
@@ -623,7 +623,7 @@
       </c>
       <c r="C3" s="4">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>19</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="C4" s="4">
         <f ca="1">+C3+7</f>
-        <v>46126</v>
+        <v>46147</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>20</v>
@@ -653,7 +653,7 @@
       </c>
       <c r="C5" s="4">
         <f t="shared" ref="C5:C19" ca="1" si="0">+C4+7</f>
-        <v>46133</v>
+        <v>46154</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>21</v>
@@ -668,7 +668,7 @@
       </c>
       <c r="C6" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46140</v>
+        <v>46161</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>22</v>
@@ -683,7 +683,7 @@
       </c>
       <c r="C7" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46147</v>
+        <v>46168</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>23</v>
@@ -698,7 +698,7 @@
       </c>
       <c r="C8" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46154</v>
+        <v>46175</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>41</v>
@@ -713,7 +713,7 @@
       </c>
       <c r="C9" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46161</v>
+        <v>46182</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>40</v>
@@ -728,7 +728,7 @@
       </c>
       <c r="C10" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46168</v>
+        <v>46189</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>24</v>
@@ -743,12 +743,12 @@
       </c>
       <c r="C11" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46175</v>
+        <v>46196</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="C12" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46182</v>
+        <v>46203</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="7" t="s">
         <v>26</v>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="C13" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46189</v>
+        <v>46210</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>27</v>
@@ -788,12 +788,12 @@
       </c>
       <c r="C14" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46196</v>
+        <v>46217</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="7" t="s">
         <v>30</v>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C15" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46203</v>
+        <v>46224</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>29</v>
@@ -818,7 +818,7 @@
       </c>
       <c r="C16" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46210</v>
+        <v>46231</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>30</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="C17" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46217</v>
+        <v>46238</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>31</v>
@@ -848,7 +848,7 @@
       </c>
       <c r="C18" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46224</v>
+        <v>46245</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>32</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="C19" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>46231</v>
+        <v>46252</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>33</v>
